--- a/EA_MONITOR_TEMPLATE.xlsx
+++ b/EA_MONITOR_TEMPLATE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EA_LAB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A05A20D-9485-4E06-ACD8-887B1380C6DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4956C40-D901-4B01-AD36-F8373FD3A8DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="28800" windowHeight="11295" activeTab="2" xr2:uid="{34B254D8-48B1-4E75-8C1F-3916B7A412D7}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="28800" windowHeight="11295" activeTab="2" xr2:uid="{3FFE4256-47BD-42C8-A52E-2407F04A43A7}"/>
   </bookViews>
   <sheets>
     <sheet name="BASELINE" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="56">
   <si>
     <t>EA</t>
   </si>
@@ -82,7 +82,7 @@
     <t>grid</t>
   </si>
   <si>
-    <t>fixed 0.01; read magic from .set</t>
+    <t>magic NOT in .set - read from MT5 GUI then fill col D</t>
   </si>
   <si>
     <t>NuiIndy RSI+ADX</t>
@@ -118,9 +118,6 @@
     <t>scalper</t>
   </si>
   <si>
-    <t>default magic-read GUI; ruin 1.9%</t>
-  </si>
-  <si>
     <t>EA_BREAKOUT_XAU Bars55</t>
   </si>
   <si>
@@ -136,7 +133,7 @@
     <t>EA_RUNNER_ST03 replica</t>
   </si>
   <si>
-    <t>deploy 2026-06-29</t>
+    <t>PROVISIONAL - re-confirm OOS (sibling overfit)</t>
   </si>
   <si>
     <t>EA_BREAKOUT_XAU Bars8</t>
@@ -151,25 +148,34 @@
     <t>symbol</t>
   </si>
   <si>
+    <t>trades</t>
+  </si>
+  <si>
     <t>net</t>
   </si>
   <si>
-    <t>trades</t>
-  </si>
-  <si>
     <t>PF</t>
   </si>
   <si>
     <t>win_pct</t>
   </si>
   <si>
-    <t>max_consec_loss</t>
-  </si>
-  <si>
-    <t>realized_dd</t>
-  </si>
-  <si>
-    <t>paste cols A-H from /ea-monitor (parse_live_deals.ps1); col I auto-fills</t>
+    <t>avg_win</t>
+  </si>
+  <si>
+    <t>avg_loss</t>
+  </si>
+  <si>
+    <t>win_loss</t>
+  </si>
+  <si>
+    <t>max_consec_L</t>
+  </si>
+  <si>
+    <t>realized_DD</t>
+  </si>
+  <si>
+    <t>paste the per-EA summary CSV (parse_live_deals.ps1 -Csv) here at A2; cols A-K match exactly; col N Key auto-fills</t>
   </si>
   <si>
     <t>BT_PF</t>
@@ -184,23 +190,29 @@
     <t>Live_trades</t>
   </si>
   <si>
-    <t>Live_DD%</t>
-  </si>
-  <si>
-    <t>BT_DD%</t>
+    <t>Live_net</t>
+  </si>
+  <si>
+    <t>Live_DD</t>
   </si>
   <si>
     <t>FLAG</t>
   </si>
   <si>
-    <t>FLAG = analysis only, NOT auto-reject. Reject = /ea-monitor judgment (magic attribution + mechanism). KEEP PF&gt;=0.7xBT; &lt;10 trades=INCONCLUSIVE; 10-24=WATCH; &gt;=25 and PF&lt;0.7xBT=PAUSE-review.</t>
+    <t>FLAG = analysis only, NOT auto-reject. Reject = /ea-monitor judgment (magic attribution + mechanism).</t>
+  </si>
+  <si>
+    <t>Thresholds: KEEP PF&gt;=0.7xBT; &lt;10 trades=INCONCLUSIVE; 10-24=WATCH; &gt;=25 and PF&lt;0.7xBT=PAUSE-review. Live_DD (col I) shown for reference (not in FLAG yet; fill BT_maxDD% to compare).</t>
+  </si>
+  <si>
+    <t>MG_v1 + Gold Reaper magic not in .set -&gt; fill BASELINE col D from MT5 GUI or they stay SET MAGIC.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -213,6 +225,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -243,7 +256,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
     <dxf>
       <fill>
         <patternFill>
@@ -262,6 +275,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF9BC2E6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -601,23 +621,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7C3862C-6AC4-42E1-B94B-9B89A15B6F81}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BE0980C-2AB2-4F8C-8A1B-11FF96DB839F}">
   <dimension ref="A1:J10"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="47.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" ht="15">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -649,7 +669,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -673,7 +693,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -697,7 +717,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -721,7 +741,7 @@
         <v>2.4700000000000002</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -745,7 +765,7 @@
         <v>2.62</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -766,12 +786,12 @@
         <v>2.0699999999999998</v>
       </c>
       <c r="J6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>27</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
@@ -787,18 +807,18 @@
         <v>991001|XAUUSD</v>
       </c>
       <c r="F7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G7">
         <v>2.94</v>
       </c>
       <c r="J7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" t="s">
-        <v>30</v>
       </c>
       <c r="B8" t="s">
         <v>20</v>
@@ -814,15 +834,15 @@
         <v>990005|GBPUSD</v>
       </c>
       <c r="F8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G8">
         <v>2.08</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
         <v>20</v>
@@ -844,12 +864,12 @@
         <v>3.93</v>
       </c>
       <c r="J9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" t="s">
-        <v>33</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
@@ -865,13 +885,13 @@
         <v>991002|XAUUSD</v>
       </c>
       <c r="F10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G10">
         <v>3.92</v>
       </c>
       <c r="J10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -880,404 +900,416 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3A070B7-E8DB-4329-A8B6-97C62F18E68E}">
-  <dimension ref="A1:K60"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89FE26FE-0E70-406E-BDFA-6664CA2EF867}">
+  <dimension ref="A1:P60"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="58.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="102" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" ht="15">
+    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
-      <c r="I2" t="str">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N2" t="str">
         <f>IF(A2="","",A2&amp;"|"&amp;B2)</f>
         <v/>
       </c>
-      <c r="K2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="I3" t="str">
+      <c r="P2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N3" t="str">
         <f>IF(A3="","",A3&amp;"|"&amp;B3)</f>
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:11">
-      <c r="I4" t="str">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N4" t="str">
         <f>IF(A4="","",A4&amp;"|"&amp;B4)</f>
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:11">
-      <c r="I5" t="str">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N5" t="str">
         <f>IF(A5="","",A5&amp;"|"&amp;B5)</f>
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:11">
-      <c r="I6" t="str">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N6" t="str">
         <f>IF(A6="","",A6&amp;"|"&amp;B6)</f>
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:11">
-      <c r="I7" t="str">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N7" t="str">
         <f>IF(A7="","",A7&amp;"|"&amp;B7)</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:11">
-      <c r="I8" t="str">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N8" t="str">
         <f>IF(A8="","",A8&amp;"|"&amp;B8)</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:11">
-      <c r="I9" t="str">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N9" t="str">
         <f>IF(A9="","",A9&amp;"|"&amp;B9)</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:11">
-      <c r="I10" t="str">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N10" t="str">
         <f>IF(A10="","",A10&amp;"|"&amp;B10)</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:11">
-      <c r="I11" t="str">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N11" t="str">
         <f>IF(A11="","",A11&amp;"|"&amp;B11)</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:11">
-      <c r="I12" t="str">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N12" t="str">
         <f>IF(A12="","",A12&amp;"|"&amp;B12)</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:11">
-      <c r="I13" t="str">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N13" t="str">
         <f>IF(A13="","",A13&amp;"|"&amp;B13)</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:11">
-      <c r="I14" t="str">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N14" t="str">
         <f>IF(A14="","",A14&amp;"|"&amp;B14)</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:11">
-      <c r="I15" t="str">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N15" t="str">
         <f>IF(A15="","",A15&amp;"|"&amp;B15)</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:11">
-      <c r="I16" t="str">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N16" t="str">
         <f>IF(A16="","",A16&amp;"|"&amp;B16)</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="9:9">
-      <c r="I17" t="str">
+    <row r="17" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N17" t="str">
         <f>IF(A17="","",A17&amp;"|"&amp;B17)</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="9:9">
-      <c r="I18" t="str">
+    <row r="18" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N18" t="str">
         <f>IF(A18="","",A18&amp;"|"&amp;B18)</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="9:9">
-      <c r="I19" t="str">
+    <row r="19" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N19" t="str">
         <f>IF(A19="","",A19&amp;"|"&amp;B19)</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="9:9">
-      <c r="I20" t="str">
+    <row r="20" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N20" t="str">
         <f>IF(A20="","",A20&amp;"|"&amp;B20)</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="9:9">
-      <c r="I21" t="str">
+    <row r="21" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N21" t="str">
         <f>IF(A21="","",A21&amp;"|"&amp;B21)</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="9:9">
-      <c r="I22" t="str">
+    <row r="22" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N22" t="str">
         <f>IF(A22="","",A22&amp;"|"&amp;B22)</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="9:9">
-      <c r="I23" t="str">
+    <row r="23" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N23" t="str">
         <f>IF(A23="","",A23&amp;"|"&amp;B23)</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="9:9">
-      <c r="I24" t="str">
+    <row r="24" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N24" t="str">
         <f>IF(A24="","",A24&amp;"|"&amp;B24)</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="9:9">
-      <c r="I25" t="str">
+    <row r="25" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N25" t="str">
         <f>IF(A25="","",A25&amp;"|"&amp;B25)</f>
         <v/>
       </c>
     </row>
-    <row r="26" spans="9:9">
-      <c r="I26" t="str">
+    <row r="26" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N26" t="str">
         <f>IF(A26="","",A26&amp;"|"&amp;B26)</f>
         <v/>
       </c>
     </row>
-    <row r="27" spans="9:9">
-      <c r="I27" t="str">
+    <row r="27" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N27" t="str">
         <f>IF(A27="","",A27&amp;"|"&amp;B27)</f>
         <v/>
       </c>
     </row>
-    <row r="28" spans="9:9">
-      <c r="I28" t="str">
+    <row r="28" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N28" t="str">
         <f>IF(A28="","",A28&amp;"|"&amp;B28)</f>
         <v/>
       </c>
     </row>
-    <row r="29" spans="9:9">
-      <c r="I29" t="str">
+    <row r="29" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N29" t="str">
         <f>IF(A29="","",A29&amp;"|"&amp;B29)</f>
         <v/>
       </c>
     </row>
-    <row r="30" spans="9:9">
-      <c r="I30" t="str">
+    <row r="30" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N30" t="str">
         <f>IF(A30="","",A30&amp;"|"&amp;B30)</f>
         <v/>
       </c>
     </row>
-    <row r="31" spans="9:9">
-      <c r="I31" t="str">
+    <row r="31" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N31" t="str">
         <f>IF(A31="","",A31&amp;"|"&amp;B31)</f>
         <v/>
       </c>
     </row>
-    <row r="32" spans="9:9">
-      <c r="I32" t="str">
+    <row r="32" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N32" t="str">
         <f>IF(A32="","",A32&amp;"|"&amp;B32)</f>
         <v/>
       </c>
     </row>
-    <row r="33" spans="9:9">
-      <c r="I33" t="str">
+    <row r="33" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N33" t="str">
         <f>IF(A33="","",A33&amp;"|"&amp;B33)</f>
         <v/>
       </c>
     </row>
-    <row r="34" spans="9:9">
-      <c r="I34" t="str">
+    <row r="34" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N34" t="str">
         <f>IF(A34="","",A34&amp;"|"&amp;B34)</f>
         <v/>
       </c>
     </row>
-    <row r="35" spans="9:9">
-      <c r="I35" t="str">
+    <row r="35" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N35" t="str">
         <f>IF(A35="","",A35&amp;"|"&amp;B35)</f>
         <v/>
       </c>
     </row>
-    <row r="36" spans="9:9">
-      <c r="I36" t="str">
+    <row r="36" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N36" t="str">
         <f>IF(A36="","",A36&amp;"|"&amp;B36)</f>
         <v/>
       </c>
     </row>
-    <row r="37" spans="9:9">
-      <c r="I37" t="str">
+    <row r="37" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N37" t="str">
         <f>IF(A37="","",A37&amp;"|"&amp;B37)</f>
         <v/>
       </c>
     </row>
-    <row r="38" spans="9:9">
-      <c r="I38" t="str">
+    <row r="38" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N38" t="str">
         <f>IF(A38="","",A38&amp;"|"&amp;B38)</f>
         <v/>
       </c>
     </row>
-    <row r="39" spans="9:9">
-      <c r="I39" t="str">
+    <row r="39" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N39" t="str">
         <f>IF(A39="","",A39&amp;"|"&amp;B39)</f>
         <v/>
       </c>
     </row>
-    <row r="40" spans="9:9">
-      <c r="I40" t="str">
+    <row r="40" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N40" t="str">
         <f>IF(A40="","",A40&amp;"|"&amp;B40)</f>
         <v/>
       </c>
     </row>
-    <row r="41" spans="9:9">
-      <c r="I41" t="str">
+    <row r="41" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N41" t="str">
         <f>IF(A41="","",A41&amp;"|"&amp;B41)</f>
         <v/>
       </c>
     </row>
-    <row r="42" spans="9:9">
-      <c r="I42" t="str">
+    <row r="42" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N42" t="str">
         <f>IF(A42="","",A42&amp;"|"&amp;B42)</f>
         <v/>
       </c>
     </row>
-    <row r="43" spans="9:9">
-      <c r="I43" t="str">
+    <row r="43" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N43" t="str">
         <f>IF(A43="","",A43&amp;"|"&amp;B43)</f>
         <v/>
       </c>
     </row>
-    <row r="44" spans="9:9">
-      <c r="I44" t="str">
+    <row r="44" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N44" t="str">
         <f>IF(A44="","",A44&amp;"|"&amp;B44)</f>
         <v/>
       </c>
     </row>
-    <row r="45" spans="9:9">
-      <c r="I45" t="str">
+    <row r="45" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N45" t="str">
         <f>IF(A45="","",A45&amp;"|"&amp;B45)</f>
         <v/>
       </c>
     </row>
-    <row r="46" spans="9:9">
-      <c r="I46" t="str">
+    <row r="46" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N46" t="str">
         <f>IF(A46="","",A46&amp;"|"&amp;B46)</f>
         <v/>
       </c>
     </row>
-    <row r="47" spans="9:9">
-      <c r="I47" t="str">
+    <row r="47" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N47" t="str">
         <f>IF(A47="","",A47&amp;"|"&amp;B47)</f>
         <v/>
       </c>
     </row>
-    <row r="48" spans="9:9">
-      <c r="I48" t="str">
+    <row r="48" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N48" t="str">
         <f>IF(A48="","",A48&amp;"|"&amp;B48)</f>
         <v/>
       </c>
     </row>
-    <row r="49" spans="9:9">
-      <c r="I49" t="str">
+    <row r="49" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N49" t="str">
         <f>IF(A49="","",A49&amp;"|"&amp;B49)</f>
         <v/>
       </c>
     </row>
-    <row r="50" spans="9:9">
-      <c r="I50" t="str">
+    <row r="50" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N50" t="str">
         <f>IF(A50="","",A50&amp;"|"&amp;B50)</f>
         <v/>
       </c>
     </row>
-    <row r="51" spans="9:9">
-      <c r="I51" t="str">
+    <row r="51" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N51" t="str">
         <f>IF(A51="","",A51&amp;"|"&amp;B51)</f>
         <v/>
       </c>
     </row>
-    <row r="52" spans="9:9">
-      <c r="I52" t="str">
+    <row r="52" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N52" t="str">
         <f>IF(A52="","",A52&amp;"|"&amp;B52)</f>
         <v/>
       </c>
     </row>
-    <row r="53" spans="9:9">
-      <c r="I53" t="str">
+    <row r="53" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N53" t="str">
         <f>IF(A53="","",A53&amp;"|"&amp;B53)</f>
         <v/>
       </c>
     </row>
-    <row r="54" spans="9:9">
-      <c r="I54" t="str">
+    <row r="54" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N54" t="str">
         <f>IF(A54="","",A54&amp;"|"&amp;B54)</f>
         <v/>
       </c>
     </row>
-    <row r="55" spans="9:9">
-      <c r="I55" t="str">
+    <row r="55" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N55" t="str">
         <f>IF(A55="","",A55&amp;"|"&amp;B55)</f>
         <v/>
       </c>
     </row>
-    <row r="56" spans="9:9">
-      <c r="I56" t="str">
+    <row r="56" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N56" t="str">
         <f>IF(A56="","",A56&amp;"|"&amp;B56)</f>
         <v/>
       </c>
     </row>
-    <row r="57" spans="9:9">
-      <c r="I57" t="str">
+    <row r="57" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N57" t="str">
         <f>IF(A57="","",A57&amp;"|"&amp;B57)</f>
         <v/>
       </c>
     </row>
-    <row r="58" spans="9:9">
-      <c r="I58" t="str">
+    <row r="58" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N58" t="str">
         <f>IF(A58="","",A58&amp;"|"&amp;B58)</f>
         <v/>
       </c>
     </row>
-    <row r="59" spans="9:9">
-      <c r="I59" t="str">
+    <row r="59" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N59" t="str">
         <f>IF(A59="","",A59&amp;"|"&amp;B59)</f>
         <v/>
       </c>
     </row>
-    <row r="60" spans="9:9">
-      <c r="I60" t="str">
+    <row r="60" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N60" t="str">
         <f>IF(A60="","",A60&amp;"|"&amp;B60)</f>
         <v/>
       </c>
@@ -1288,23 +1320,23 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF02B5E6-66E1-423F-B6E7-BB34E16A8E11}">
-  <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E58F933B-3B17-4DDD-AF38-61E3DCA2D6C1}">
+  <dimension ref="A1:J14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="176.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="170.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" ht="15">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1315,28 +1347,28 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
         <f>BASELINE!A2</f>
         <v>Matchagrid MG_v1</v>
@@ -1353,32 +1385,32 @@
         <f>BASELINE!G2</f>
         <v>2.08</v>
       </c>
-      <c r="E2">
-        <f>IFERROR(INDEX(LIVE!$E:$E,MATCH(C2,LIVE!$I:$I,0)),"")</f>
-        <v>0</v>
-      </c>
-      <c r="F2">
+      <c r="E2" t="str">
+        <f>IF(C2="","(set magic)",IFERROR(INDEX(LIVE!$E:$E,MATCH(C2,LIVE!$N:$N,0)),""))</f>
+        <v>(set magic)</v>
+      </c>
+      <c r="F2" t="str">
         <f>IFERROR(E2/D2,"")</f>
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <f>IFERROR(INDEX(LIVE!$D:$D,MATCH(C2,LIVE!$I:$I,0)),"")</f>
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <f>IFERROR(INDEX(LIVE!$H:$H,MATCH(C2,LIVE!$I:$I,0)),"")</f>
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <f>BASELINE!H2</f>
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <f>IF(C2="","",IFERROR(INDEX(LIVE!$C:$C,MATCH(C2,LIVE!$N:$N,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <f>IF(C2="","",IFERROR(INDEX(LIVE!$D:$D,MATCH(C2,LIVE!$N:$N,0)),""))</f>
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <f>IF(C2="","",IFERROR(INDEX(LIVE!$K:$K,MATCH(C2,LIVE!$N:$N,0)),""))</f>
+        <v/>
       </c>
       <c r="J2" t="str">
-        <f>IF(G2="","NO DATA",IF(G2&lt;10,"INCONCLUSIVE",IF(F2&gt;=0.7,"KEEP",IF(G2&lt;25,"WATCH","PAUSE-review"))))</f>
-        <v>INCONCLUSIVE</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <f>IF(C2="","SET MAGIC",IF(G2="","NO DATA",IF(G2&lt;10,"INCONCLUSIVE",IF(F2&gt;=0.7,"KEEP",IF(G2&lt;25,"WATCH","PAUSE-review")))))</f>
+        <v>SET MAGIC</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>BASELINE!A3</f>
         <v>NuiIndy RSI+ADX</v>
@@ -1396,7 +1428,7 @@
         <v>2</v>
       </c>
       <c r="E3" t="str">
-        <f>IFERROR(INDEX(LIVE!$E:$E,MATCH(C3,LIVE!$I:$I,0)),"")</f>
+        <f>IF(C3="","(set magic)",IFERROR(INDEX(LIVE!$E:$E,MATCH(C3,LIVE!$N:$N,0)),""))</f>
         <v/>
       </c>
       <c r="F3" t="str">
@@ -1404,23 +1436,23 @@
         <v/>
       </c>
       <c r="G3" t="str">
-        <f>IFERROR(INDEX(LIVE!$D:$D,MATCH(C3,LIVE!$I:$I,0)),"")</f>
+        <f>IF(C3="","",IFERROR(INDEX(LIVE!$C:$C,MATCH(C3,LIVE!$N:$N,0)),""))</f>
         <v/>
       </c>
       <c r="H3" t="str">
-        <f>IFERROR(INDEX(LIVE!$H:$H,MATCH(C3,LIVE!$I:$I,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I3">
-        <f>BASELINE!H3</f>
-        <v>0</v>
+        <f>IF(C3="","",IFERROR(INDEX(LIVE!$D:$D,MATCH(C3,LIVE!$N:$N,0)),""))</f>
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <f>IF(C3="","",IFERROR(INDEX(LIVE!$K:$K,MATCH(C3,LIVE!$N:$N,0)),""))</f>
+        <v/>
       </c>
       <c r="J3" t="str">
-        <f>IF(G3="","NO DATA",IF(G3&lt;10,"INCONCLUSIVE",IF(F3&gt;=0.7,"KEEP",IF(G3&lt;25,"WATCH","PAUSE-review"))))</f>
+        <f>IF(C3="","SET MAGIC",IF(G3="","NO DATA",IF(G3&lt;10,"INCONCLUSIVE",IF(F3&gt;=0.7,"KEEP",IF(G3&lt;25,"WATCH","PAUSE-review")))))</f>
         <v>NO DATA</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>BASELINE!A4</f>
         <v>ST_EA03 MACD</v>
@@ -1438,7 +1470,7 @@
         <v>2.4700000000000002</v>
       </c>
       <c r="E4" t="str">
-        <f>IFERROR(INDEX(LIVE!$E:$E,MATCH(C4,LIVE!$I:$I,0)),"")</f>
+        <f>IF(C4="","(set magic)",IFERROR(INDEX(LIVE!$E:$E,MATCH(C4,LIVE!$N:$N,0)),""))</f>
         <v/>
       </c>
       <c r="F4" t="str">
@@ -1446,23 +1478,23 @@
         <v/>
       </c>
       <c r="G4" t="str">
-        <f>IFERROR(INDEX(LIVE!$D:$D,MATCH(C4,LIVE!$I:$I,0)),"")</f>
+        <f>IF(C4="","",IFERROR(INDEX(LIVE!$C:$C,MATCH(C4,LIVE!$N:$N,0)),""))</f>
         <v/>
       </c>
       <c r="H4" t="str">
-        <f>IFERROR(INDEX(LIVE!$H:$H,MATCH(C4,LIVE!$I:$I,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I4">
-        <f>BASELINE!H4</f>
-        <v>0</v>
+        <f>IF(C4="","",IFERROR(INDEX(LIVE!$D:$D,MATCH(C4,LIVE!$N:$N,0)),""))</f>
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <f>IF(C4="","",IFERROR(INDEX(LIVE!$K:$K,MATCH(C4,LIVE!$N:$N,0)),""))</f>
+        <v/>
       </c>
       <c r="J4" t="str">
-        <f>IF(G4="","NO DATA",IF(G4&lt;10,"INCONCLUSIVE",IF(F4&gt;=0.7,"KEEP",IF(G4&lt;25,"WATCH","PAUSE-review"))))</f>
+        <f>IF(C4="","SET MAGIC",IF(G4="","NO DATA",IF(G4&lt;10,"INCONCLUSIVE",IF(F4&gt;=0.7,"KEEP",IF(G4&lt;25,"WATCH","PAUSE-review")))))</f>
         <v>NO DATA</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>BASELINE!A5</f>
         <v>ST_EA03 MACD</v>
@@ -1480,7 +1512,7 @@
         <v>2.62</v>
       </c>
       <c r="E5" t="str">
-        <f>IFERROR(INDEX(LIVE!$E:$E,MATCH(C5,LIVE!$I:$I,0)),"")</f>
+        <f>IF(C5="","(set magic)",IFERROR(INDEX(LIVE!$E:$E,MATCH(C5,LIVE!$N:$N,0)),""))</f>
         <v/>
       </c>
       <c r="F5" t="str">
@@ -1488,23 +1520,23 @@
         <v/>
       </c>
       <c r="G5" t="str">
-        <f>IFERROR(INDEX(LIVE!$D:$D,MATCH(C5,LIVE!$I:$I,0)),"")</f>
+        <f>IF(C5="","",IFERROR(INDEX(LIVE!$C:$C,MATCH(C5,LIVE!$N:$N,0)),""))</f>
         <v/>
       </c>
       <c r="H5" t="str">
-        <f>IFERROR(INDEX(LIVE!$H:$H,MATCH(C5,LIVE!$I:$I,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I5">
-        <f>BASELINE!H5</f>
-        <v>0</v>
+        <f>IF(C5="","",IFERROR(INDEX(LIVE!$D:$D,MATCH(C5,LIVE!$N:$N,0)),""))</f>
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <f>IF(C5="","",IFERROR(INDEX(LIVE!$K:$K,MATCH(C5,LIVE!$N:$N,0)),""))</f>
+        <v/>
       </c>
       <c r="J5" t="str">
-        <f>IF(G5="","NO DATA",IF(G5&lt;10,"INCONCLUSIVE",IF(F5&gt;=0.7,"KEEP",IF(G5&lt;25,"WATCH","PAUSE-review"))))</f>
+        <f>IF(C5="","SET MAGIC",IF(G5="","NO DATA",IF(G5&lt;10,"INCONCLUSIVE",IF(F5&gt;=0.7,"KEEP",IF(G5&lt;25,"WATCH","PAUSE-review")))))</f>
         <v>NO DATA</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>BASELINE!A6</f>
         <v>Gold Reaper 4.3</v>
@@ -1521,32 +1553,32 @@
         <f>BASELINE!G6</f>
         <v>2.0699999999999998</v>
       </c>
-      <c r="E6">
-        <f>IFERROR(INDEX(LIVE!$E:$E,MATCH(C6,LIVE!$I:$I,0)),"")</f>
-        <v>0</v>
-      </c>
-      <c r="F6">
+      <c r="E6" t="str">
+        <f>IF(C6="","(set magic)",IFERROR(INDEX(LIVE!$E:$E,MATCH(C6,LIVE!$N:$N,0)),""))</f>
+        <v>(set magic)</v>
+      </c>
+      <c r="F6" t="str">
         <f>IFERROR(E6/D6,"")</f>
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <f>IFERROR(INDEX(LIVE!$D:$D,MATCH(C6,LIVE!$I:$I,0)),"")</f>
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <f>IFERROR(INDEX(LIVE!$H:$H,MATCH(C6,LIVE!$I:$I,0)),"")</f>
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <f>BASELINE!H6</f>
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <f>IF(C6="","",IFERROR(INDEX(LIVE!$C:$C,MATCH(C6,LIVE!$N:$N,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <f>IF(C6="","",IFERROR(INDEX(LIVE!$D:$D,MATCH(C6,LIVE!$N:$N,0)),""))</f>
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <f>IF(C6="","",IFERROR(INDEX(LIVE!$K:$K,MATCH(C6,LIVE!$N:$N,0)),""))</f>
+        <v/>
       </c>
       <c r="J6" t="str">
-        <f>IF(G6="","NO DATA",IF(G6&lt;10,"INCONCLUSIVE",IF(F6&gt;=0.7,"KEEP",IF(G6&lt;25,"WATCH","PAUSE-review"))))</f>
-        <v>INCONCLUSIVE</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <f>IF(C6="","SET MAGIC",IF(G6="","NO DATA",IF(G6&lt;10,"INCONCLUSIVE",IF(F6&gt;=0.7,"KEEP",IF(G6&lt;25,"WATCH","PAUSE-review")))))</f>
+        <v>SET MAGIC</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>BASELINE!A7</f>
         <v>EA_BREAKOUT_XAU Bars55</v>
@@ -1564,7 +1596,7 @@
         <v>2.94</v>
       </c>
       <c r="E7" t="str">
-        <f>IFERROR(INDEX(LIVE!$E:$E,MATCH(C7,LIVE!$I:$I,0)),"")</f>
+        <f>IF(C7="","(set magic)",IFERROR(INDEX(LIVE!$E:$E,MATCH(C7,LIVE!$N:$N,0)),""))</f>
         <v/>
       </c>
       <c r="F7" t="str">
@@ -1572,23 +1604,23 @@
         <v/>
       </c>
       <c r="G7" t="str">
-        <f>IFERROR(INDEX(LIVE!$D:$D,MATCH(C7,LIVE!$I:$I,0)),"")</f>
+        <f>IF(C7="","",IFERROR(INDEX(LIVE!$C:$C,MATCH(C7,LIVE!$N:$N,0)),""))</f>
         <v/>
       </c>
       <c r="H7" t="str">
-        <f>IFERROR(INDEX(LIVE!$H:$H,MATCH(C7,LIVE!$I:$I,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I7">
-        <f>BASELINE!H7</f>
-        <v>0</v>
+        <f>IF(C7="","",IFERROR(INDEX(LIVE!$D:$D,MATCH(C7,LIVE!$N:$N,0)),""))</f>
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <f>IF(C7="","",IFERROR(INDEX(LIVE!$K:$K,MATCH(C7,LIVE!$N:$N,0)),""))</f>
+        <v/>
       </c>
       <c r="J7" t="str">
-        <f>IF(G7="","NO DATA",IF(G7&lt;10,"INCONCLUSIVE",IF(F7&gt;=0.7,"KEEP",IF(G7&lt;25,"WATCH","PAUSE-review"))))</f>
+        <f>IF(C7="","SET MAGIC",IF(G7="","NO DATA",IF(G7&lt;10,"INCONCLUSIVE",IF(F7&gt;=0.7,"KEEP",IF(G7&lt;25,"WATCH","PAUSE-review")))))</f>
         <v>NO DATA</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>BASELINE!A8</f>
         <v>LondonConsoBreakout CB_GBP</v>
@@ -1606,7 +1638,7 @@
         <v>2.08</v>
       </c>
       <c r="E8" t="str">
-        <f>IFERROR(INDEX(LIVE!$E:$E,MATCH(C8,LIVE!$I:$I,0)),"")</f>
+        <f>IF(C8="","(set magic)",IFERROR(INDEX(LIVE!$E:$E,MATCH(C8,LIVE!$N:$N,0)),""))</f>
         <v/>
       </c>
       <c r="F8" t="str">
@@ -1614,23 +1646,23 @@
         <v/>
       </c>
       <c r="G8" t="str">
-        <f>IFERROR(INDEX(LIVE!$D:$D,MATCH(C8,LIVE!$I:$I,0)),"")</f>
+        <f>IF(C8="","",IFERROR(INDEX(LIVE!$C:$C,MATCH(C8,LIVE!$N:$N,0)),""))</f>
         <v/>
       </c>
       <c r="H8" t="str">
-        <f>IFERROR(INDEX(LIVE!$H:$H,MATCH(C8,LIVE!$I:$I,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I8">
-        <f>BASELINE!H8</f>
-        <v>0</v>
+        <f>IF(C8="","",IFERROR(INDEX(LIVE!$D:$D,MATCH(C8,LIVE!$N:$N,0)),""))</f>
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <f>IF(C8="","",IFERROR(INDEX(LIVE!$K:$K,MATCH(C8,LIVE!$N:$N,0)),""))</f>
+        <v/>
       </c>
       <c r="J8" t="str">
-        <f>IF(G8="","NO DATA",IF(G8&lt;10,"INCONCLUSIVE",IF(F8&gt;=0.7,"KEEP",IF(G8&lt;25,"WATCH","PAUSE-review"))))</f>
+        <f>IF(C8="","SET MAGIC",IF(G8="","NO DATA",IF(G8&lt;10,"INCONCLUSIVE",IF(F8&gt;=0.7,"KEEP",IF(G8&lt;25,"WATCH","PAUSE-review")))))</f>
         <v>NO DATA</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>BASELINE!A9</f>
         <v>EA_RUNNER_ST03 replica</v>
@@ -1648,7 +1680,7 @@
         <v>3.93</v>
       </c>
       <c r="E9" t="str">
-        <f>IFERROR(INDEX(LIVE!$E:$E,MATCH(C9,LIVE!$I:$I,0)),"")</f>
+        <f>IF(C9="","(set magic)",IFERROR(INDEX(LIVE!$E:$E,MATCH(C9,LIVE!$N:$N,0)),""))</f>
         <v/>
       </c>
       <c r="F9" t="str">
@@ -1656,23 +1688,23 @@
         <v/>
       </c>
       <c r="G9" t="str">
-        <f>IFERROR(INDEX(LIVE!$D:$D,MATCH(C9,LIVE!$I:$I,0)),"")</f>
+        <f>IF(C9="","",IFERROR(INDEX(LIVE!$C:$C,MATCH(C9,LIVE!$N:$N,0)),""))</f>
         <v/>
       </c>
       <c r="H9" t="str">
-        <f>IFERROR(INDEX(LIVE!$H:$H,MATCH(C9,LIVE!$I:$I,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I9">
-        <f>BASELINE!H9</f>
-        <v>0</v>
+        <f>IF(C9="","",IFERROR(INDEX(LIVE!$D:$D,MATCH(C9,LIVE!$N:$N,0)),""))</f>
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <f>IF(C9="","",IFERROR(INDEX(LIVE!$K:$K,MATCH(C9,LIVE!$N:$N,0)),""))</f>
+        <v/>
       </c>
       <c r="J9" t="str">
-        <f>IF(G9="","NO DATA",IF(G9&lt;10,"INCONCLUSIVE",IF(F9&gt;=0.7,"KEEP",IF(G9&lt;25,"WATCH","PAUSE-review"))))</f>
+        <f>IF(C9="","SET MAGIC",IF(G9="","NO DATA",IF(G9&lt;10,"INCONCLUSIVE",IF(F9&gt;=0.7,"KEEP",IF(G9&lt;25,"WATCH","PAUSE-review")))))</f>
         <v>NO DATA</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>BASELINE!A10</f>
         <v>EA_BREAKOUT_XAU Bars8</v>
@@ -1690,7 +1722,7 @@
         <v>3.92</v>
       </c>
       <c r="E10" t="str">
-        <f>IFERROR(INDEX(LIVE!$E:$E,MATCH(C10,LIVE!$I:$I,0)),"")</f>
+        <f>IF(C10="","(set magic)",IFERROR(INDEX(LIVE!$E:$E,MATCH(C10,LIVE!$N:$N,0)),""))</f>
         <v/>
       </c>
       <c r="F10" t="str">
@@ -1698,39 +1730,52 @@
         <v/>
       </c>
       <c r="G10" t="str">
-        <f>IFERROR(INDEX(LIVE!$D:$D,MATCH(C10,LIVE!$I:$I,0)),"")</f>
+        <f>IF(C10="","",IFERROR(INDEX(LIVE!$C:$C,MATCH(C10,LIVE!$N:$N,0)),""))</f>
         <v/>
       </c>
       <c r="H10" t="str">
-        <f>IFERROR(INDEX(LIVE!$H:$H,MATCH(C10,LIVE!$I:$I,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I10">
-        <f>BASELINE!H10</f>
-        <v>0</v>
+        <f>IF(C10="","",IFERROR(INDEX(LIVE!$D:$D,MATCH(C10,LIVE!$N:$N,0)),""))</f>
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <f>IF(C10="","",IFERROR(INDEX(LIVE!$K:$K,MATCH(C10,LIVE!$N:$N,0)),""))</f>
+        <v/>
       </c>
       <c r="J10" t="str">
-        <f>IF(G10="","NO DATA",IF(G10&lt;10,"INCONCLUSIVE",IF(F10&gt;=0.7,"KEEP",IF(G10&lt;25,"WATCH","PAUSE-review"))))</f>
+        <f>IF(C10="","SET MAGIC",IF(G10="","NO DATA",IF(G10&lt;10,"INCONCLUSIVE",IF(F10&gt;=0.7,"KEEP",IF(G10&lt;25,"WATCH","PAUSE-review")))))</f>
         <v>NO DATA</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J2:J10">
-    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="1" stopIfTrue="1">
       <formula>$J2="INCONCLUSIVE"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="2" stopIfTrue="1">
+      <formula>$J2="SET MAGIC"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="3" stopIfTrue="1">
       <formula>$J2="KEEP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="4" stopIfTrue="1">
       <formula>$J2="PAUSE-review"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="5" stopIfTrue="1">
       <formula>$J2="WATCH"</formula>
     </cfRule>
   </conditionalFormatting>
